--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,60 +909,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133648602</v>
+        <v>137102020</v>
       </c>
       <c r="B4" t="n">
-        <v>58563</v>
+        <v>56948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102987</v>
+        <v>100088</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Toftmossen, Toftmossen, Vstm</t>
+          <t>Långtalbo, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572282</v>
+        <v>572315</v>
       </c>
       <c r="R4" t="n">
-        <v>6619828</v>
+        <v>6619800</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,19 +977,14 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>04:51</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:12</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Adult</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,77 +999,77 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133648602</t>
+          <t>https://artportalen.se/Sighting/137102020</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134320430</v>
+        <v>133648602</v>
       </c>
       <c r="B5" t="n">
-        <v>58250</v>
+        <v>58563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103019</v>
+        <v>102987</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärtmes</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aegithalos caudatus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Toftmossen, Vstm</t>
+          <t>Toftmossen, Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572289</v>
+        <v>572282</v>
       </c>
       <c r="R5" t="n">
-        <v>6619829</v>
+        <v>6619828</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>04:53</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>04:57</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,67 +1123,63 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134320430</t>
+          <t>https://artportalen.se/Sighting/133648602</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100195745</v>
+        <v>134320430</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>58250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103019</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572282</v>
+        <v>572289</v>
       </c>
       <c r="R6" t="n">
-        <v>6619885</v>
+        <v>6619829</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,12 +1217,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,41 +1241,30 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog, inslag av björk</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>I mosstäcke</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100195745</t>
+          <t>https://artportalen.se/Sighting/134320430</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104436824</v>
+        <v>100195745</v>
       </c>
       <c r="B7" t="n">
         <v>99118</v>
@@ -1329,13 +1307,15 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Toftmossen (knärot), Vstm</t>
+          <t>Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572278</v>
+        <v>572282</v>
       </c>
       <c r="R7" t="n">
         <v>6619885</v>
@@ -1363,11 +1343,6 @@
           <t>Sura</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>U-Sur-0476</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2022-04-23</t>
@@ -1384,18 +1359,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>mosstäcke, gammal barrblandskog, inslag av björk</t>
+          <t>Gammal barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>I mosstäcke</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1403,46 +1384,46 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104436824</t>
+          <t>https://artportalen.se/Sighting/100195745</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4172247</v>
+        <v>104436824</v>
       </c>
       <c r="B8" t="n">
-        <v>97977</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,16 +1431,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Toftmossen, Vstm</t>
+          <t>Toftmossen (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572227</v>
+        <v>572278</v>
       </c>
       <c r="R8" t="n">
-        <v>6619874</v>
+        <v>6619885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,14 +1470,19 @@
           <t>Sura</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>U-Sur-0476</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-05-02</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-05-02</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,38 +1496,37 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Ungskog på torvbrytningsområde</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Torvmark</t>
+          <t>mosstäcke, gammal barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4172247</t>
+          <t>https://artportalen.se/Sighting/104436824</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100195762</v>
+        <v>4172247</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>97977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,38 +1534,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572282</v>
+        <v>572227</v>
       </c>
       <c r="R9" t="n">
-        <v>6619885</v>
+        <v>6619874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,12 +1593,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2011-05-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2011-05-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,13 +1607,17 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, inslag av björk</t>
+          <t>Ungskog på torvbrytningsområde</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Torvmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1638,6 +1633,222 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4172247</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137102018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98218</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtalbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572444</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619994</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flertal mindre bestånd längs 8-10 m</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137102018</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100195762</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Toftmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572282</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619885</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/100195762</t>
         </is>
@@ -1653,6 +1864,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137102020</v>
       </c>
       <c r="B4" t="n">
-        <v>56948</v>
+        <v>56961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137102020</v>
       </c>
       <c r="B4" t="n">
-        <v>56961</v>
+        <v>56963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98247</v>
+        <v>98250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137102020</v>
       </c>
       <c r="B4" t="n">
-        <v>56963</v>
+        <v>56973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98250</v>
+        <v>98260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98260</v>
+        <v>98261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137102020</v>
       </c>
       <c r="B4" t="n">
-        <v>56973</v>
+        <v>56974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98261</v>
+        <v>98266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98266</v>
+        <v>98268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98268</v>
+        <v>98274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98274</v>
+        <v>98286</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98286</v>
+        <v>98287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98287</v>
+        <v>98290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>137102020</v>
       </c>
       <c r="B4" t="n">
-        <v>56974</v>
+        <v>56977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>137102018</v>
       </c>
       <c r="B10" t="n">
-        <v>98290</v>
+        <v>98294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
